--- a/coaching_forms/016_wellness_coaching_interest_survey--coaching_forms.xlsx
+++ b/coaching_forms/016_wellness_coaching_interest_survey--coaching_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>currently_seeking_coach</t>
+          <t>currently seeking coach</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>not_seeking_coach</t>
+          <t>not seeking coach</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>self_improvement</t>
+          <t>self improvement</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>non_binary</t>
+          <t>non binary</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>in person</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bi_weekly</t>
+          <t>bi weekly</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>non_binary</t>
+          <t>non binary</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>certification_1</t>
+          <t>certification 1</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>certification_2</t>
+          <t>certification 2</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>certification_3</t>
+          <t>certification 3</t>
         </is>
       </c>
     </row>
